--- a/extenbooks/S512.xlsx
+++ b/extenbooks/S512.xlsx
@@ -447,11 +447,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B44"/>
+  <dimension ref="A1:D71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -465,6 +467,16 @@
           <t>S&amp;T 1994, units=share</t>
         </is>
       </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>, units=share</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>BLS CES, units=share</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -475,6 +487,16 @@
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>S512-A</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>S512-COMBINED</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>S512-EXT</t>
         </is>
       </c>
     </row>
@@ -485,6 +507,12 @@
       <c r="B3" s="3" t="n">
         <v>0.54</v>
       </c>
+      <c r="C3" s="3" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -493,6 +521,12 @@
       <c r="B4" s="3" t="n">
         <v>0.535</v>
       </c>
+      <c r="C4" s="3" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -501,6 +535,12 @@
       <c r="B5" s="3" t="n">
         <v>0.53</v>
       </c>
+      <c r="C5" s="3" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -509,6 +549,12 @@
       <c r="B6" s="3" t="n">
         <v>0.525</v>
       </c>
+      <c r="C6" s="3" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -517,6 +563,12 @@
       <c r="B7" s="3" t="n">
         <v>0.52</v>
       </c>
+      <c r="C7" s="3" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -525,6 +577,12 @@
       <c r="B8" s="3" t="n">
         <v>0.515</v>
       </c>
+      <c r="C8" s="3" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -533,6 +591,12 @@
       <c r="B9" s="3" t="n">
         <v>0.51</v>
       </c>
+      <c r="C9" s="3" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -541,6 +605,12 @@
       <c r="B10" s="3" t="n">
         <v>0.505</v>
       </c>
+      <c r="C10" s="3" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -549,6 +619,12 @@
       <c r="B11" s="3" t="n">
         <v>0.5</v>
       </c>
+      <c r="C11" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -557,6 +633,12 @@
       <c r="B12" s="3" t="n">
         <v>0.495</v>
       </c>
+      <c r="C12" s="3" t="n">
+        <v>0.495</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -565,6 +647,12 @@
       <c r="B13" s="3" t="n">
         <v>0.49</v>
       </c>
+      <c r="C13" s="3" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -573,6 +661,12 @@
       <c r="B14" s="3" t="n">
         <v>0.485</v>
       </c>
+      <c r="C14" s="3" t="n">
+        <v>0.485</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -581,6 +675,12 @@
       <c r="B15" s="3" t="n">
         <v>0.48</v>
       </c>
+      <c r="C15" s="3" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -589,6 +689,12 @@
       <c r="B16" s="3" t="n">
         <v>0.476</v>
       </c>
+      <c r="C16" s="3" t="n">
+        <v>0.476</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -597,6 +703,12 @@
       <c r="B17" s="3" t="n">
         <v>0.472</v>
       </c>
+      <c r="C17" s="3" t="n">
+        <v>0.472</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -605,6 +717,12 @@
       <c r="B18" s="3" t="n">
         <v>0.468</v>
       </c>
+      <c r="C18" s="3" t="n">
+        <v>0.468</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -613,6 +731,12 @@
       <c r="B19" s="3" t="n">
         <v>0.464</v>
       </c>
+      <c r="C19" s="3" t="n">
+        <v>0.464</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -621,6 +745,12 @@
       <c r="B20" s="3" t="n">
         <v>0.46</v>
       </c>
+      <c r="C20" s="3" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -629,13 +759,25 @@
       <c r="B21" s="3" t="n">
         <v>0.456</v>
       </c>
+      <c r="C21" s="3" t="n">
+        <v>0.456</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
         <v>1967</v>
       </c>
       <c r="B22" s="3" t="n">
-        <v>0.452</v>
+        <v>0.42</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="23">
@@ -645,6 +787,12 @@
       <c r="B23" s="3" t="n">
         <v>0.448</v>
       </c>
+      <c r="C23" s="3" t="n">
+        <v>0.448</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -653,6 +801,12 @@
       <c r="B24" s="3" t="n">
         <v>0.444</v>
       </c>
+      <c r="C24" s="3" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -661,6 +815,12 @@
       <c r="B25" s="3" t="n">
         <v>0.44</v>
       </c>
+      <c r="C25" s="3" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -669,6 +829,12 @@
       <c r="B26" s="3" t="n">
         <v>0.436</v>
       </c>
+      <c r="C26" s="3" t="n">
+        <v>0.436</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -677,6 +843,12 @@
       <c r="B27" s="3" t="n">
         <v>0.432</v>
       </c>
+      <c r="C27" s="3" t="n">
+        <v>0.432</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -685,6 +857,12 @@
       <c r="B28" s="3" t="n">
         <v>0.428</v>
       </c>
+      <c r="C28" s="3" t="n">
+        <v>0.428</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -693,6 +871,12 @@
       <c r="B29" s="3" t="n">
         <v>0.424</v>
       </c>
+      <c r="C29" s="3" t="n">
+        <v>0.424</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -701,6 +885,12 @@
       <c r="B30" s="3" t="n">
         <v>0.42</v>
       </c>
+      <c r="C30" s="3" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -709,6 +899,12 @@
       <c r="B31" s="3" t="n">
         <v>0.416</v>
       </c>
+      <c r="C31" s="3" t="n">
+        <v>0.416</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -717,6 +913,12 @@
       <c r="B32" s="3" t="n">
         <v>0.412</v>
       </c>
+      <c r="C32" s="3" t="n">
+        <v>0.412</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -725,6 +927,12 @@
       <c r="B33" s="3" t="n">
         <v>0.408</v>
       </c>
+      <c r="C33" s="3" t="n">
+        <v>0.408</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -733,6 +941,12 @@
       <c r="B34" s="3" t="n">
         <v>0.404</v>
       </c>
+      <c r="C34" s="3" t="n">
+        <v>0.404</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -741,6 +955,12 @@
       <c r="B35" s="3" t="n">
         <v>0.4</v>
       </c>
+      <c r="C35" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -749,6 +969,12 @@
       <c r="B36" s="3" t="n">
         <v>0.396</v>
       </c>
+      <c r="C36" s="3" t="n">
+        <v>0.396</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -757,6 +983,12 @@
       <c r="B37" s="3" t="n">
         <v>0.391</v>
       </c>
+      <c r="C37" s="3" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -765,6 +997,12 @@
       <c r="B38" s="3" t="n">
         <v>0.387</v>
       </c>
+      <c r="C38" s="3" t="n">
+        <v>0.387</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -773,6 +1011,12 @@
       <c r="B39" s="3" t="n">
         <v>0.382</v>
       </c>
+      <c r="C39" s="3" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -781,6 +1025,12 @@
       <c r="B40" s="3" t="n">
         <v>0.378</v>
       </c>
+      <c r="C40" s="3" t="n">
+        <v>0.378</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -789,6 +1039,12 @@
       <c r="B41" s="3" t="n">
         <v>0.373</v>
       </c>
+      <c r="C41" s="3" t="n">
+        <v>0.373</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -797,6 +1053,12 @@
       <c r="B42" s="3" t="n">
         <v>0.369</v>
       </c>
+      <c r="C42" s="3" t="n">
+        <v>0.369</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -805,6 +1067,12 @@
       <c r="B43" s="3" t="n">
         <v>0.364</v>
       </c>
+      <c r="C43" s="3" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -812,6 +1080,390 @@
       </c>
       <c r="B44" s="3" t="n">
         <v>0.36</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>1998</v>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>0.3194999999999999</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>0.3194999999999999</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>1999</v>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>0.3165114284735395</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>0.3165114284735395</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>0.3117114433591545</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>0.3117114433591545</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>2001</v>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>0.3004424626351077</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>0.3004424626351077</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>2002</v>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>0.2884424367957939</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>0.2884424367957939</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>2003</v>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>0.2807348720050808</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>0.2807348720050808</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>0.2778160604544648</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>0.2778160604544648</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>0.2754358301928286</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>0.2754358301928286</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>2006</v>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>0.2738621271830954</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>0.2738621271830954</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>2007</v>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>0.2697375441649561</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>0.2697375441649561</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>2008</v>
+      </c>
+      <c r="B55" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>0.2631146660255516</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>0.2631146660255516</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>2009</v>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>0.2450153902631809</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>0.2450153902631809</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>2010</v>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>0.2392116640452947</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>0.2392116640452947</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>0.2400754547243566</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>0.2400754547243566</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B59" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>0.2418850197157117</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>0.2418850197157117</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>0.2415144726693874</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>0.2415144726693874</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B61" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>0.2434564922503259</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>0.2434564922503259</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>0.2424603107168807</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>0.2424603107168807</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B63" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>0.2401236453001887</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>0.2401236453001887</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>0.2408035254901317</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>0.2408035254901317</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B65" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>0.2423167237469966</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>0.2423167237469966</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B66" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>0.2427769599629248</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>0.2427769599629248</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B67" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>0.2370259718008288</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>0.2370259718008288</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B68" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>0.2331839705668378</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>0.2331839705668378</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B69" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>0.2359342620674729</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>0.2359342620674729</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B70" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>0.2357955671744271</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>0.2357955671744271</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B71" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>0.2350377147803383</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>0.2350377147803383</v>
       </c>
     </row>
   </sheetData>
@@ -825,7 +1477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B84"/>
+  <dimension ref="A1:B89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -924,7 +1576,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1948–2024</t>
+          <t>1948-1989</t>
         </is>
       </c>
     </row>
@@ -948,7 +1600,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Fig_9_3</t>
+          <t>Fig_9_3, Fig_5_8</t>
         </is>
       </c>
     </row>
@@ -990,386 +1642,391 @@
     </row>
     <row r="14"/>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Subseries</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>source / role</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>S512-A</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>S&amp;T 1994</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>S512-EXT</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>BLS CES</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>S512-COMBINED</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>DPR (markdown)</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t># S512 — Productive Wage Share (V*/W)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>**Chapter**: 5 — The Marxian Categories: Empirical Estimates</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>**Source Table**: Appendix 5.7</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>**Units**: share</t>
-        </is>
-      </c>
+      <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>**Period**: 1948-1989 (book period; extension via BEA NIPA + BLS CES when API access provisioned)</t>
+          <t># S512 — Productive Wage Share (V*/W)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>**Content Type**: time_series</t>
-        </is>
-      </c>
+      <c r="B22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>**Status**: book_period_validated</t>
+          <t>**Chapter**: 5 — The Marxian Categories: Empirical Estimates</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>**Source Table**: Appendix 5.7</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>**Units**: share</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>**Period**: 1948-1989 (book period; extension via BEA NIPA + BLS CES when API access provisioned)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>## Definition</t>
+          <t>**Content Type**: time_series</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>**Status**: book_period_validated</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Productive Wage Share (V*/W). The share of total wage bill paid to productive labor. Feeds the e = 1.238/(V*/W) - 1 extension formula for S506.</t>
-        </is>
-      </c>
+      <c r="B29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="B31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>## Definition</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>## Subseries</t>
-        </is>
-      </c>
+      <c r="B33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
-      <c r="B34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Productive Wage Share (V*/W). The share of total wage bill paid to productive labor. Feeds the e = 1.238/(V*/W) - 1 extension formula for S506.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>| Subseries | Source | Period | Units |</t>
-        </is>
-      </c>
+      <c r="B35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>|---|---|---|---|</t>
+          <t>---</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>| `S512-A` | S&amp;T 1994 | 1948-1989 | share |</t>
-        </is>
-      </c>
+      <c r="B37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>| `S512-EXT` | BLS CES | 1990-2024 | share |</t>
+          <t>## Subseries</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>| `S512-COMBINED` |  | 1948-2024 | share |</t>
-        </is>
-      </c>
+      <c r="B39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
-      <c r="B40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>| Subseries | Source | Period | Units |</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>|---|---|---|---|</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
-      <c r="B42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>| `S512-A` | S&amp;T 1994 | 1948-1989 | share |</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>## Construction</t>
+          <t>| `S512-EXT` | BLS CES | 1990-2024 | share |</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
-      <c r="B44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>| `S512-COMBINED` |  | 1948-2024 | share |</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>### S512-A (book period, 1948-1989)</t>
-        </is>
-      </c>
+      <c r="B45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
-      <c r="B46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>1. Read `data/source/book_tables/Table5_7_KeyRatios.csv`.</t>
-        </is>
-      </c>
+      <c r="B47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2. Extract column `T512A` (book-authoritative values; the `T512` column without the A-suffix is the replicator-recomputed comparison and is not used here).</t>
+          <t>## Construction</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>3. No further transformation — this is the canonical published value.</t>
-        </is>
-      </c>
+      <c r="B49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
-      <c r="B50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>### S512-A (book period, 1948-1989)</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Validator checks the loaded series against the published benchmark years from validation_config.json.</t>
-        </is>
-      </c>
+      <c r="B51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr"/>
-      <c r="B52" t="inlineStr"/>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>1. Read `data/source/book_tables/Table5_7_KeyRatios.csv`.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>2. Extract column `T512A` (book-authoritative values; the `T512` column without the A-suffix is the replicator-recomputed comparison and is not used here).</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
-      <c r="B54" t="inlineStr"/>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>3. No further transformation — this is the canonical published value.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>## Reference Values (Validation Benchmarks)</t>
-        </is>
-      </c>
+      <c r="B55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr"/>
-      <c r="B56" t="inlineStr"/>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Validator checks the loaded series against the published benchmark years from validation_config.json.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr"/>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>1948=0.54, 1958=0.49, 1967=0.452, 1977=0.412, 1989=0.36</t>
-        </is>
-      </c>
+      <c r="B57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr"/>
-      <c r="B58" t="inlineStr"/>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr"/>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Tolerance class: `share_series` (rel 0.05 / abs 0.02).</t>
-        </is>
-      </c>
+      <c r="B59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr"/>
-      <c r="B60" t="inlineStr"/>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>## Reference Values (Validation Benchmarks)</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr"/>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Validator: `code/V03_validators/V03_S512_productive_wage_share.py` writes to `data/intermediate/validation/S512.json`.</t>
-        </is>
-      </c>
+      <c r="B61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr"/>
-      <c r="B62" t="inlineStr"/>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>1948=0.54, 1958=0.49, 1967=0.452, 1977=0.412, 1989=0.36</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr"/>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="B63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr"/>
-      <c r="B64" t="inlineStr"/>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Tolerance class: `share_series` (rel 0.05 / abs 0.02).</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr"/>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>## Provenance Chain</t>
-        </is>
-      </c>
+      <c r="B65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr"/>
-      <c r="B66" t="inlineStr"/>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Validator: `code/V03_validators/V03_S512_productive_wage_share.py` writes to `data/intermediate/validation/S512.json`.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr"/>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>```</t>
-        </is>
-      </c>
+      <c r="B67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr">
         <is>
-          <t>data/source/book_tables/Table5_7_KeyRatios.csv</t>
+          <t>---</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr"/>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  └── code/L01_loaders/L01_S512_productive_wage_share.py</t>
-        </is>
-      </c>
+      <c r="B69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
-          <t xml:space="preserve">       └── data/intermediate/S512.csv</t>
+          <t>## Provenance Chain</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr"/>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            └── code/P02_processors/P02_S512_productive_wage_share.py</t>
-        </is>
-      </c>
+      <c r="B71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
-          <t xml:space="preserve">                 └── data/final/S512.csv</t>
+          <t>```</t>
         </is>
       </c>
     </row>
@@ -1377,7 +2034,7 @@
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr">
         <is>
-          <t xml:space="preserve">                      └── code/V03_validators/V03_S512_productive_wage_share.py</t>
+          <t>data/source/book_tables/Table5_7_KeyRatios.csv</t>
         </is>
       </c>
     </row>
@@ -1385,65 +2042,105 @@
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="inlineStr">
         <is>
-          <t>```</t>
+          <t xml:space="preserve">  └── code/L01_loaders/L01_S512_productive_wage_share.py</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr"/>
-      <c r="B75" t="inlineStr"/>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       └── data/intermediate/S512.csv</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="inlineStr">
         <is>
-          <t>---</t>
+          <t xml:space="preserve">            └── code/P02_processors/P02_S512_productive_wage_share.py</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr"/>
-      <c r="B77" t="inlineStr"/>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                 └── data/final/S512.csv</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr">
         <is>
-          <t>## Citations</t>
+          <t xml:space="preserve">                      └── code/V03_validators/V03_S512_productive_wage_share.py</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr"/>
-      <c r="B79" t="inlineStr"/>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>```</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr"/>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. *Measuring the Wealth of Nations: The Political Economy of National Accounts*. Cambridge University Press. Table 5.7 (Key Ratios), Chapter 5.</t>
-        </is>
-      </c>
+      <c r="B80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr"/>
-      <c r="B81" t="inlineStr"/>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr"/>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="B82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr"/>
-      <c r="B83" t="inlineStr"/>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>## Citations</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr"/>
-      <c r="B84" t="inlineStr">
+      <c r="B84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr"/>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. *Measuring the Wealth of Nations: The Political Economy of National Accounts*. Cambridge University Press. Table 5.7 (Key Ratios), Chapter 5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr"/>
+      <c r="B86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr"/>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr"/>
+      <c r="B88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr"/>
+      <c r="B89" t="inlineStr">
         <is>
           <t>*Generated by anu-ingestion (re-authored from scratch against the Anu Framework v10.0 standard).*</t>
         </is>
@@ -1460,10 +2157,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
     <col width="62" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1488,226 +2185,356 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>methodology_description</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>V*/W = variable capital / total employee compensation. Under the approximation ec_u/ec_p ≈ 1 (where ec is employee compensation per worker), V*/W ≈ Lp/L. This approximation is central to the extension methodology: V*/W is proxied by the productive labor share.</t>
+          <t>V_j ≡ ec_j · (Lp)_j ≡ (Wp)_j = variable capital in the jth production sector; V* ≡ Wp = ∑ (Wp)_j = total variable capital.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ST_1994, Ch5 p.113; Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_14/full_transcription.md</t>
+          <t>ST_1994</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>benchmark_values</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Book benchmarks from Table 5.7: 1948=0.54, 1967=0.45, 1989=0.36. These track close to but slightly below Lp/L values, confirming the ec_u/ec_p ≈ 1 approximation (it is actually slightly &gt; 1).</t>
+          <t>Figures 5.10 and 5.11 make quite explicit that the unit wages of productive and unproductive workers change only slightly, whereas their relative employments change drastically. We can therefore unambiguously conclude that the relative decline in productive to total wages Wp/W (= V*/W) is almost entirely due to the relative decline in productive to total employment Lp/L.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ST_1994, Table 5.7; Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_16/full_transcription.md</t>
+          <t>ST_1994</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>figure_context</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Fig 9.3 uses V*/W in the profit rate decomposition, showing how the productive wage share mediates between the exploitation rate and the overall profit rate.</t>
+          <t>At the beginning of the postwar period the wage of unproductive workers is some 11%-12% higher than that of productive workers, but this relative advantage gradually disappears until, by the end of the period, unproductive wages are 3%-4% lower than productive wages.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ST_1994, Fig 9.3; Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_13/full_transcription.md</t>
+          <t>ST_1994</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>approximation_analysis</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The V*/W ≈ Lp/L approximation holds when unproductive and productive workers earn similar per-capita compensation. Empirically, V*/W is slightly below Lp/L (0.54 vs 0.57 in 1948; 0.36 vs 0.36 in 1989), suggesting ec_u/ec_p has converged toward 1 over time.</t>
+          <t>V*/W, 42%, -33%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ST_1994, Ch5 p.113; Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_15/full_transcription.md</t>
+          <t>ST_1994</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>external_comparison</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mohun's unproductive decomposition data (mohun_unproductive_decomposition*.csv) allows computing alternative V*/W estimates under his broader productive classification. His productive sector includes Information and retail eating/drinking.</t>
+          <t>Figure 5.8 contrasts the levels of real variable capital and of the total real wage bill. Their absolute growth is greater than that of the corresponding labor totals in Figure 5.7 because the wage measures also incorporate the effects of growing real wages. But the relative movements of wage and employment measures is virtually the same, as is evident in Figure 5.9. V*/W declines by 34%, while Lp/L declines by 37%.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mohun_2013; Inputs/ExternalSources/Mohun/</t>
+          <t>ST_1994</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>caveat</t>
+          <t>methodology_description</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>V*/W is the key input to S504 (V*) and S506 (e) extensions. Any error in V*/W propagates multiplicatively through the entire distributional analysis. Post-1989 wage inequality trends may cause ec_u/ec_p to diverge from 1.</t>
+          <t>V*/W = variable capital / total employee compensation. Under the approximation ec_u/ec_p ≈ 1 (where ec is employee compensation per worker), V*/W ≈ Lp/L. This approximation is central to the extension methodology: V*/W is proxied by the productive labor share.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DPR T512_DPR.md; EPR T512_EPR.md</t>
+          <t>ST_1994, Ch5 p.113; Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_14/full_transcription.md</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>decision_reference</t>
+          <t>benchmark_values</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DEC-005: BLS CES production/nonsupervisory worker ratios are used as the proxy for IO-based productive/unproductive labor decomposition when extending S512. S512 extension is certified at 76% faithfulness (CERTIFIED WITH NOTES). Cross-validated against Mohun (2005) estimates.</t>
+          <t>Book benchmarks from Table 5.7: 1948=0.54, 1967=0.45, 1989=0.36. These track close to but slightly below Lp/L values, confirming the ec_u/ec_p ≈ 1 approximation (it is actually slightly &gt; 1).</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DECISION_LOG.md#DEC-005</t>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
+          <t>ST_1994, Table 5.7; Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_16/full_transcription.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>figure_context</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Fig 9.3 uses V*/W in the profit rate decomposition, showing how the productive wage share mediates between the exploitation rate and the overall profit rate.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ST_1994, Fig 9.3; Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_13/full_transcription.md</t>
+        </is>
+      </c>
+    </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>methodology_summary</t>
+          <t>approximation_analysis</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Productive wage share V*/W ≈ Lp/L under the ec_u/ec_p ≈ 1 approximation. Book benchmarks decline from 0.54 (1948) to 0.36 (1989). Critical input to S504 and S506 extensions. Extended via BLS CES proxy (DEC-005, faithfulness 76%).</t>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
+          <t>The V*/W ≈ Lp/L approximation holds when unproductive and productive workers earn similar per-capita compensation. Empirically, V*/W is slightly below Lp/L (0.54 vs 0.57 in 1948; 0.36 vs 0.36 in 1989), suggesting ec_u/ec_p has converged toward 1 over time.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ST_1994, Ch5 p.113; Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_15/full_transcription.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>external_comparison</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Mohun's unproductive decomposition data (mohun_unproductive_decomposition*.csv) allows computing alternative V*/W estimates under his broader productive classification. His productive sector includes Information and retail eating/drinking.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Mohun_2013; Inputs/ExternalSources/Mohun/</t>
+        </is>
+      </c>
+    </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>known_issues:</t>
+          <t>caveat</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>V*/W is the key input to S504 (V*) and S506 (e) extensions. Any error in V*/W propagates multiplicatively through the entire distributional analysis. Post-1989 wage inequality trends may cause ec_u/ec_p to diverge from 1.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>DPR T512_DPR.md; EPR T512_EPR.md</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>decision_reference</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ec_u/ec_p ≈ 1 may deteriorate with rising wage inequality post-1989</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr"/>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Error propagates multiplicatively to S504 and S506</t>
-        </is>
-      </c>
-    </row>
+          <t>[internal-decision-record]: BLS CES production/nonsupervisory worker ratios are used as the proxy for IO-based productive/unproductive labor decomposition when extending S512. S512 extension is certified at 76% faithfulness (CERTIFIED WITH NOTES). Cross-validated against Mohun (2005) estimates.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>[internal-decision-log]#[internal-decision-record]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Only 3 benchmark years available (1948, 1967, 1989)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16"/>
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>VERBATIM QUOTES (top-level)</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr"/>
+      <c r="C15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="n">
+        <v>113</v>
+      </c>
+    </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>cross_references:</t>
-        </is>
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="n">
+        <v>113</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>S504</t>
-        </is>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="n">
+        <v>130</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>S506</t>
-        </is>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="n">
+        <v>140</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>S511</t>
-        </is>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="n">
+        <v>113</v>
       </c>
     </row>
     <row r="21"/>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>citations:</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>ST_1994</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. Measuring the Wealth of Nations: The Political Economy of National Accounts. Cambridge University Press.</t>
-        </is>
-      </c>
-    </row>
+          <t>methodology_summary</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Productive wage share V*/W ≈ Lp/L under the ec_u/ec_p ≈ 1 approximation. Book benchmarks decline from 0.54 (1948) to 0.36 (1989). Critical input to S504 and S506 extensions. Extended via BLS CES proxy ([internal-decision-record], faithfulness 76%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>known_issues:</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ec_u/ec_p ≈ 1 may deteriorate with rising wage inequality post-1989</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Error propagates multiplicatively to S504 and S506</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Only 3 benchmark years available (1948, 1967, 1989)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>cross_references:</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>S504</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>S506</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>S511</t>
+        </is>
+      </c>
+    </row>
+    <row r="33"/>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>citations:</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>ST_1994</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. Measuring the Wealth of Nations: The Political Economy of National Accounts. Cambridge University Press.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>Mohun_2013</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>Mohun, Simon. 2013. 'Unproductive Labor in the U.S. Economy 1964-2010.' Review of Radical Political Economics 46(3): 355-379.</t>
         </is>
@@ -1724,11 +2551,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
@@ -1820,91 +2647,226 @@
     </row>
     <row r="5"/>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>EXTENSION</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
+      <c r="B6" s="4" t="inlineStr"/>
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>splice_year</t>
+          <t>api</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1989</t>
+          <t>BLS</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>splice_method</t>
+          <t>splice_year</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>1989</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>depends_on</t>
+          <t>splice_method</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
+          <t>level</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>output_subseries</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>S512-EXT</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>VALIDATION</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
+          <t>combined_subseries</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>S512-COMBINED</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>reference_values</t>
+          <t>provenance</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{"1948": 0.54, "1967": 0.46, "1989": 0.33}</t>
+          <t>{"shaikh_source": "Shaikh, A., &amp; Tonak, E. A. (1994). *Measuring the Wealth of Nations: The Political Economy of National Accounts*. Cambridge University Press., Chapter 5, Table 5.7 column V*/W (productive wage share of total wages); Appendix H.1 V_star (productive variable capital); identity V*/W = productive wages / total wages", "shaikh_appendix_ref": "Table 5.7 (V*/W, 1948-1989); Appendix H.1; cf. Figure 5.7", "extension_source": "BLS CES + BEA NIPA: production-worker wages by industry from BLS CES, aggregated through productive/unproductive concordance to compute V*; total wage bill W from BEA NIPA Table 6.2", "extension_url": "https://www.bls.gov/ces/; https://apps.bea.gov/iTable/iTable.cfm?reqid=19&amp;step=2", "conceptual_continuity": "Productive wage share V*/W is the fraction of total wages paid to productive workers (production workers in productive industries). It is a directly observable share given BLS CES production-worker hours/wages and BEA total compensation, subject to the Marxian partition. Conceptual continuity holds with the same caveats as S511.", "vintage_note": "BLS CES 2003 NAICS transition; BEA NIPA comprehensive revisions; treatment of stock-based and deferred compensation differs across vintages; productive/unproductive partition update for NAICS.", "note": "Hyper-review cleanup 2026-05-19 per Decision 0003"}</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>depends_on</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>VALIDATION</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>reference_values</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>{"1948": 0.54, "1958": 0.49, "1967": 0.42, "1977": 0.412, "1989": 0.36}</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>expected_range</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>[0.1, 0.8]</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>tolerance</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>share_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>tolerance_class</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>share_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>tolerance_rel</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>tolerance_abs</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>source_table</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Table 5.14, p.140</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>previous_1967_value</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>0.452</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>previous_1967_source</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>code-derived (pre-v1.0, linear interpolation in Table5_7_KeyRatios.csv)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>1967 midpoint anchor corrected from code-derived 0.452 (registry rounded to 0.45 in hyper-review notes) to book Table 5.14 value 0.42. Endpoints 1948/1989 preserved from Table 5.7. Drift documented in DIV-006. Note: 1958/1977 intermediate values remain code-derived linear interpolations from Table 5.7 source CSV; only the 1967 midpoint has a directly-quoted book anchor in Table 5.14 (p.140).</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S512.xlsx
+++ b/extenbooks/S512.xlsx
@@ -447,13 +447,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:E79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -464,17 +465,22 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>S&amp;T 1994, units=share</t>
+          <t>S&amp;T 1994, units=per_subseries</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>, units=share</t>
+          <t>, units=per_subseries</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>BLS CES, units=share</t>
+          <t>BLS CES, units=per_subseries</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>derived, units=per_subseries</t>
         </is>
       </c>
     </row>
@@ -497,6 +503,11 @@
       <c r="D2" s="2" t="inlineStr">
         <is>
           <t>S512-EXT</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>S512-INTERP</t>
         </is>
       </c>
     </row>
@@ -513,18 +524,24 @@
       <c r="D3" s="3" t="n">
         <v/>
       </c>
+      <c r="E3" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>1949</v>
       </c>
       <c r="B4" s="3" t="n">
-        <v>0.535</v>
+        <v>0.52</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0.535</v>
+        <v>0.52</v>
       </c>
       <c r="D4" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E4" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -533,12 +550,15 @@
         <v>1950</v>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0.53</v>
+        <v>0.52</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>0.53</v>
+        <v>0.52</v>
       </c>
       <c r="D5" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E5" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -547,12 +567,15 @@
         <v>1951</v>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0.525</v>
+        <v>0.51</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>0.525</v>
+        <v>0.51</v>
       </c>
       <c r="D6" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E6" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -561,12 +584,15 @@
         <v>1952</v>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="D7" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E7" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -575,12 +601,15 @@
         <v>1953</v>
       </c>
       <c r="B8" s="3" t="n">
-        <v>0.515</v>
+        <v>0.5</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>0.515</v>
+        <v>0.5</v>
       </c>
       <c r="D8" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E8" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -589,12 +618,15 @@
         <v>1954</v>
       </c>
       <c r="B9" s="3" t="n">
-        <v>0.51</v>
+        <v>0.48</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0.51</v>
+        <v>0.48</v>
       </c>
       <c r="D9" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E9" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -603,12 +635,15 @@
         <v>1955</v>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.505</v>
+        <v>0.48</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.505</v>
+        <v>0.48</v>
       </c>
       <c r="D10" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E10" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -617,12 +652,15 @@
         <v>1956</v>
       </c>
       <c r="B11" s="3" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="D11" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E11" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -631,12 +669,15 @@
         <v>1957</v>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0.495</v>
+        <v>0.46</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0.495</v>
+        <v>0.46</v>
       </c>
       <c r="D12" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E12" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -645,12 +686,15 @@
         <v>1958</v>
       </c>
       <c r="B13" s="3" t="n">
-        <v>0.49</v>
+        <v>0.44</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0.49</v>
+        <v>0.44</v>
       </c>
       <c r="D13" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E13" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -659,12 +703,15 @@
         <v>1959</v>
       </c>
       <c r="B14" s="3" t="n">
-        <v>0.485</v>
+        <v>0.45</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0.485</v>
+        <v>0.45</v>
       </c>
       <c r="D14" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E14" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -673,12 +720,15 @@
         <v>1960</v>
       </c>
       <c r="B15" s="3" t="n">
-        <v>0.48</v>
+        <v>0.44</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>0.48</v>
+        <v>0.44</v>
       </c>
       <c r="D15" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E15" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -687,12 +737,15 @@
         <v>1961</v>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.476</v>
+        <v>0.43</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.476</v>
+        <v>0.43</v>
       </c>
       <c r="D16" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E16" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -701,12 +754,15 @@
         <v>1962</v>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.472</v>
+        <v>0.43</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0.472</v>
+        <v>0.43</v>
       </c>
       <c r="D17" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E17" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -715,12 +771,15 @@
         <v>1963</v>
       </c>
       <c r="B18" s="3" t="n">
-        <v>0.468</v>
+        <v>0.43</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>0.468</v>
+        <v>0.43</v>
       </c>
       <c r="D18" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E18" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -729,12 +788,15 @@
         <v>1964</v>
       </c>
       <c r="B19" s="3" t="n">
-        <v>0.464</v>
+        <v>0.42</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>0.464</v>
+        <v>0.42</v>
       </c>
       <c r="D19" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E19" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -743,12 +805,15 @@
         <v>1965</v>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="D20" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E20" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -757,12 +822,15 @@
         <v>1966</v>
       </c>
       <c r="B21" s="3" t="n">
-        <v>0.456</v>
+        <v>0.43</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>0.456</v>
+        <v>0.43</v>
       </c>
       <c r="D21" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E21" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -779,18 +847,24 @@
       <c r="D22" s="3" t="n">
         <v/>
       </c>
+      <c r="E22" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
         <v>1968</v>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.448</v>
+        <v>0.42</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.448</v>
+        <v>0.42</v>
       </c>
       <c r="D23" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E23" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -799,12 +873,15 @@
         <v>1969</v>
       </c>
       <c r="B24" s="3" t="n">
-        <v>0.444</v>
+        <v>0.42</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>0.444</v>
+        <v>0.42</v>
       </c>
       <c r="D24" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E24" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -813,12 +890,15 @@
         <v>1970</v>
       </c>
       <c r="B25" s="3" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="D25" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E25" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -827,12 +907,15 @@
         <v>1971</v>
       </c>
       <c r="B26" s="3" t="n">
-        <v>0.436</v>
+        <v>0.4</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>0.436</v>
+        <v>0.4</v>
       </c>
       <c r="D26" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E26" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -841,12 +924,15 @@
         <v>1972</v>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.432</v>
+        <v>0.41</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.432</v>
+        <v>0.41</v>
       </c>
       <c r="D27" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E27" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -855,12 +941,15 @@
         <v>1973</v>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0.428</v>
+        <v>0.42</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0.428</v>
+        <v>0.42</v>
       </c>
       <c r="D28" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E28" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -869,12 +958,15 @@
         <v>1974</v>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.424</v>
+        <v>0.41</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.424</v>
+        <v>0.41</v>
       </c>
       <c r="D29" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E29" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -883,12 +975,15 @@
         <v>1975</v>
       </c>
       <c r="B30" s="3" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="D30" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E30" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -897,12 +992,15 @@
         <v>1976</v>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0.416</v>
+        <v>0.4</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0.416</v>
+        <v>0.4</v>
       </c>
       <c r="D31" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E31" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -911,12 +1009,15 @@
         <v>1977</v>
       </c>
       <c r="B32" s="3" t="n">
-        <v>0.412</v>
+        <v>0.41</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>0.412</v>
+        <v>0.41</v>
       </c>
       <c r="D32" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E32" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -925,12 +1026,15 @@
         <v>1978</v>
       </c>
       <c r="B33" s="3" t="n">
-        <v>0.408</v>
+        <v>0.41</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>0.408</v>
+        <v>0.41</v>
       </c>
       <c r="D33" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E33" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -939,12 +1043,15 @@
         <v>1979</v>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0.404</v>
+        <v>0.41</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0.404</v>
+        <v>0.41</v>
       </c>
       <c r="D34" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E34" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -961,18 +1068,24 @@
       <c r="D35" s="3" t="n">
         <v/>
       </c>
+      <c r="E35" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
         <v>1981</v>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.396</v>
+        <v>0.39</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.396</v>
+        <v>0.39</v>
       </c>
       <c r="D36" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E36" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -981,12 +1094,15 @@
         <v>1982</v>
       </c>
       <c r="B37" s="3" t="n">
-        <v>0.391</v>
+        <v>0.38</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>0.391</v>
+        <v>0.38</v>
       </c>
       <c r="D37" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E37" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -995,12 +1111,15 @@
         <v>1983</v>
       </c>
       <c r="B38" s="3" t="n">
-        <v>0.387</v>
+        <v>0.38</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>0.387</v>
+        <v>0.38</v>
       </c>
       <c r="D38" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E38" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -1009,12 +1128,15 @@
         <v>1984</v>
       </c>
       <c r="B39" s="3" t="n">
-        <v>0.382</v>
+        <v>0.39</v>
       </c>
       <c r="C39" s="3" t="n">
-        <v>0.382</v>
+        <v>0.39</v>
       </c>
       <c r="D39" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E39" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -1023,12 +1145,15 @@
         <v>1985</v>
       </c>
       <c r="B40" s="3" t="n">
-        <v>0.378</v>
+        <v>0.38</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>0.378</v>
+        <v>0.38</v>
       </c>
       <c r="D40" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E40" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -1037,12 +1162,15 @@
         <v>1986</v>
       </c>
       <c r="B41" s="3" t="n">
-        <v>0.373</v>
+        <v>0.37</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>0.373</v>
+        <v>0.37</v>
       </c>
       <c r="D41" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E41" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -1051,12 +1179,15 @@
         <v>1987</v>
       </c>
       <c r="B42" s="3" t="n">
-        <v>0.369</v>
+        <v>0.36</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>0.369</v>
+        <v>0.36</v>
       </c>
       <c r="D42" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E42" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -1065,12 +1196,15 @@
         <v>1988</v>
       </c>
       <c r="B43" s="3" t="n">
-        <v>0.364</v>
+        <v>0.36</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>0.364</v>
+        <v>0.36</v>
       </c>
       <c r="D43" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E43" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -1087,383 +1221,603 @@
       <c r="D44" s="3" t="n">
         <v/>
       </c>
+      <c r="E44" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>1998</v>
+        <v>1990</v>
       </c>
       <c r="B45" s="3" t="n">
         <v/>
       </c>
       <c r="C45" s="3" t="n">
-        <v>0.3194999999999999</v>
+        <v>0.3546981726853149</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>0.3194999999999999</v>
+        <v/>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>0.3546981726853149</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>1999</v>
+        <v>1991</v>
       </c>
       <c r="B46" s="3" t="n">
         <v/>
       </c>
       <c r="C46" s="3" t="n">
-        <v>0.3165114284735395</v>
+        <v>0.3494744269619487</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>0.3165114284735395</v>
+        <v/>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>0.3494744269619487</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>2000</v>
+        <v>1992</v>
       </c>
       <c r="B47" s="3" t="n">
         <v/>
       </c>
       <c r="C47" s="3" t="n">
-        <v>0.3117114433591545</v>
+        <v>0.34432761289903</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>0.3117114433591545</v>
+        <v/>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>0.34432761289903</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>2001</v>
+        <v>1993</v>
       </c>
       <c r="B48" s="3" t="n">
         <v/>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.3004424626351077</v>
+        <v>0.3392565975010623</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.3004424626351077</v>
+        <v/>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>0.3392565975010623</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>2002</v>
+        <v>1994</v>
       </c>
       <c r="B49" s="3" t="n">
         <v/>
       </c>
       <c r="C49" s="3" t="n">
-        <v>0.2884424367957939</v>
+        <v>0.3342602644585117</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>0.2884424367957939</v>
+        <v/>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>0.3342602644585117</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>2003</v>
+        <v>1995</v>
       </c>
       <c r="B50" s="3" t="n">
         <v/>
       </c>
       <c r="C50" s="3" t="n">
-        <v>0.2807348720050808</v>
+        <v>0.3293375139020673</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>0.2807348720050808</v>
+        <v/>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>0.3293375139020673</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>2004</v>
+        <v>1996</v>
       </c>
       <c r="B51" s="3" t="n">
         <v/>
       </c>
       <c r="C51" s="3" t="n">
-        <v>0.2778160604544648</v>
+        <v>0.3244872621605218</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>0.2778160604544648</v>
+        <v/>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>0.3244872621605218</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>2005</v>
+        <v>1997</v>
       </c>
       <c r="B52" s="3" t="n">
         <v/>
       </c>
       <c r="C52" s="3" t="n">
-        <v>0.2754358301928286</v>
+        <v>0.3197084415222162</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>0.2754358301928286</v>
+        <v/>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>0.3197084415222162</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>2006</v>
+        <v>1998</v>
       </c>
       <c r="B53" s="3" t="n">
         <v/>
       </c>
       <c r="C53" s="3" t="n">
-        <v>0.2738621271830954</v>
+        <v>0.3149999999999999</v>
       </c>
       <c r="D53" s="3" t="n">
-        <v>0.2738621271830954</v>
+        <v>0.3149999999999999</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>2007</v>
+        <v>1999</v>
       </c>
       <c r="B54" s="3" t="n">
         <v/>
       </c>
       <c r="C54" s="3" t="n">
-        <v>0.2697375441649561</v>
+        <v>0.3120535210302502</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>0.2697375441649561</v>
+        <v>0.3120535210302502</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>2008</v>
+        <v>2000</v>
       </c>
       <c r="B55" s="3" t="n">
         <v/>
       </c>
       <c r="C55" s="3" t="n">
-        <v>0.2631146660255516</v>
+        <v>0.3073211413400116</v>
       </c>
       <c r="D55" s="3" t="n">
-        <v>0.2631146660255516</v>
+        <v>0.3073211413400116</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>2009</v>
+        <v>2001</v>
       </c>
       <c r="B56" s="3" t="n">
         <v/>
       </c>
       <c r="C56" s="3" t="n">
-        <v>0.2450153902631809</v>
+        <v>0.2962108786543316</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0.2450153902631809</v>
+        <v>0.2962108786543316</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>2010</v>
+        <v>2002</v>
       </c>
       <c r="B57" s="3" t="n">
         <v/>
       </c>
       <c r="C57" s="3" t="n">
-        <v>0.2392116640452947</v>
+        <v>0.2843798672634588</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>0.2392116640452947</v>
+        <v>0.2843798672634588</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>2011</v>
+        <v>2003</v>
       </c>
       <c r="B58" s="3" t="n">
         <v/>
       </c>
       <c r="C58" s="3" t="n">
-        <v>0.2400754547243566</v>
+        <v>0.2767808597233192</v>
       </c>
       <c r="D58" s="3" t="n">
-        <v>0.2400754547243566</v>
+        <v>0.2767808597233192</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>2012</v>
+        <v>2004</v>
       </c>
       <c r="B59" s="3" t="n">
         <v/>
       </c>
       <c r="C59" s="3" t="n">
-        <v>0.2418850197157117</v>
+        <v>0.2739031581945428</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>0.2418850197157117</v>
+        <v>0.2739031581945428</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>2013</v>
+        <v>2005</v>
       </c>
       <c r="B60" s="3" t="n">
         <v/>
       </c>
       <c r="C60" s="3" t="n">
-        <v>0.2415144726693874</v>
+        <v>0.2715564523027888</v>
       </c>
       <c r="D60" s="3" t="n">
-        <v>0.2415144726693874</v>
+        <v>0.2715564523027888</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>2014</v>
+        <v>2006</v>
       </c>
       <c r="B61" s="3" t="n">
         <v/>
       </c>
       <c r="C61" s="3" t="n">
-        <v>0.2434564922503259</v>
+        <v>0.2700049141241785</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>0.2434564922503259</v>
+        <v>0.2700049141241785</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>2015</v>
+        <v>2007</v>
       </c>
       <c r="B62" s="3" t="n">
         <v/>
       </c>
       <c r="C62" s="3" t="n">
-        <v>0.2424603107168807</v>
+        <v>0.2659384238246046</v>
       </c>
       <c r="D62" s="3" t="n">
-        <v>0.2424603107168807</v>
+        <v>0.2659384238246046</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>2016</v>
+        <v>2008</v>
       </c>
       <c r="B63" s="3" t="n">
         <v/>
       </c>
       <c r="C63" s="3" t="n">
-        <v>0.2401236453001887</v>
+        <v>0.2594088256589946</v>
       </c>
       <c r="D63" s="3" t="n">
-        <v>0.2401236453001887</v>
+        <v>0.2594088256589946</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>2017</v>
+        <v>2009</v>
       </c>
       <c r="B64" s="3" t="n">
         <v/>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0.2408035254901317</v>
+        <v>0.2415644692735586</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0.2408035254901317</v>
+        <v>0.2415644692735586</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>2018</v>
+        <v>2010</v>
       </c>
       <c r="B65" s="3" t="n">
         <v/>
       </c>
       <c r="C65" s="3" t="n">
-        <v>0.2423167237469966</v>
+        <v>0.2358424856784595</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>0.2423167237469966</v>
+        <v>0.2358424856784595</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>2019</v>
+        <v>2011</v>
       </c>
       <c r="B66" s="3" t="n">
         <v/>
       </c>
       <c r="C66" s="3" t="n">
-        <v>0.2427769599629248</v>
+        <v>0.2366941102916192</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>0.2427769599629248</v>
+        <v>0.2366941102916192</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>2020</v>
+        <v>2012</v>
       </c>
       <c r="B67" s="3" t="n">
         <v/>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0.2370259718008288</v>
+        <v>0.2384781884521101</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0.2370259718008288</v>
+        <v>0.2384781884521101</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>2021</v>
+        <v>2013</v>
       </c>
       <c r="B68" s="3" t="n">
         <v/>
       </c>
       <c r="C68" s="3" t="n">
-        <v>0.2331839705668378</v>
+        <v>0.2381128603782693</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>0.2331839705668378</v>
+        <v>0.2381128603782693</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>2022</v>
+        <v>2014</v>
       </c>
       <c r="B69" s="3" t="n">
         <v/>
       </c>
       <c r="C69" s="3" t="n">
-        <v>0.2359342620674729</v>
+        <v>0.2400275275707439</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>0.2359342620674729</v>
+        <v>0.2400275275707439</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>2023</v>
+        <v>2015</v>
       </c>
       <c r="B70" s="3" t="n">
         <v/>
       </c>
       <c r="C70" s="3" t="n">
-        <v>0.2357955671744271</v>
+        <v>0.2390453767631218</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>0.2357955671744271</v>
+        <v>0.2390453767631218</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B71" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>0.2367416221269466</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>0.2367416221269466</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B72" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>0.2374119265395665</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>0.2374119265395665</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B73" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>0.2389038121449262</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>0.2389038121449262</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B74" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>0.2393575661606301</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>0.2393575661606301</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B75" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>0.233687577831803</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>0.233687577831803</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B76" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C76" s="3" t="n">
+        <v>0.2298996892912486</v>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>0.2298996892912486</v>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B77" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>0.2326112442918747</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>0.2326112442918747</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B78" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>0.2324745028480268</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>0.2324745028480268</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
         <v>2024</v>
       </c>
-      <c r="B71" s="3" t="n">
-        <v/>
-      </c>
-      <c r="C71" s="3" t="n">
-        <v>0.2350377147803383</v>
-      </c>
-      <c r="D71" s="3" t="n">
-        <v>0.2350377147803383</v>
+      <c r="B79" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>0.2317273244313195</v>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>0.2317273244313195</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -1477,7 +1831,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B89"/>
+  <dimension ref="A1:B122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1552,7 +1906,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>share</t>
+          <t>per_subseries</t>
         </is>
       </c>
     </row>
@@ -1685,40 +2039,44 @@
       </c>
       <c r="B18" t="inlineStr"/>
     </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>S512-INTERP</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>DPR (markdown)</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t># S512 — Productive Wage Share (V*/W)</t>
-        </is>
-      </c>
+      <c r="B21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t># S512 — Productive Wage Share (V*/W)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>**Chapter**: 5 — The Marxian Categories: Empirical Estimates</t>
-        </is>
-      </c>
+      <c r="B23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>**Source Table**: Appendix 5.7</t>
+          <t>**Chapter**: 5 — The Marxian Categories: Empirical Estimates</t>
         </is>
       </c>
     </row>
@@ -1726,7 +2084,7 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>**Units**: share</t>
+          <t>**Source Table**: Appendix 5.7</t>
         </is>
       </c>
     </row>
@@ -1734,7 +2092,7 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>**Period**: 1948-1989 (book period; extension via BEA NIPA + BLS CES when API access provisioned)</t>
+          <t>**Units**: share</t>
         </is>
       </c>
     </row>
@@ -1742,7 +2100,7 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>**Content Type**: time_series</t>
+          <t>**Period**: 1948-1989 (book period; extension via BEA NIPA + BLS CES when API access provisioned)</t>
         </is>
       </c>
     </row>
@@ -1750,87 +2108,87 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>**Status**: book_period_validated</t>
+          <t>**Content Type**: time_series</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>**Status**: book_period_validated</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="B30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>## Definition</t>
-        </is>
-      </c>
+      <c r="B32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>## Definition</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Productive Wage Share (V*/W). The share of total wage bill paid to productive labor. Feeds the e = 1.238/(V*/W) - 1 extension formula for S506.</t>
-        </is>
-      </c>
+      <c r="B34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
-      <c r="B35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Productive Wage Share (V*/W). The share of total wage bill paid to productive labor. Feeds the e = 1.238/(V*/W) - 1 extension formula for S506.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="B36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
-      <c r="B37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>## Subseries</t>
-        </is>
-      </c>
+      <c r="B38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
-      <c r="B39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>## Subseries</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>| Subseries | Source | Period | Units |</t>
-        </is>
-      </c>
+      <c r="B40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>|---|---|---|---|</t>
+          <t>| Subseries | Source | Period | Units |</t>
         </is>
       </c>
     </row>
@@ -1838,7 +2196,7 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>| `S512-A` | S&amp;T 1994 | 1948-1989 | share |</t>
+          <t>|---|---|---|---|</t>
         </is>
       </c>
     </row>
@@ -1846,7 +2204,7 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>| `S512-EXT` | BLS CES | 1990-2024 | share |</t>
+          <t>| `S512-A` | S&amp;T 1994 Table 5.7 (T512A) | 1948-1989 | share |</t>
         </is>
       </c>
     </row>
@@ -1854,19 +2212,23 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>| `S512-COMBINED` |  | 1948-2024 | share |</t>
+          <t>| `S512-EXT` | BEA NIPA 6.2D, level-spliced | 1998-2024 | share |</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
-      <c r="B45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>| `S512-INTERP` | Log-linear interp between S512-A(1989) and S512-EXT(1998) | 1990-1997 | share |</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>| `S512-COMBINED` | S512-A ∪ S512-INTERP ∪ S512-EXT | 1948-2024 | share |</t>
         </is>
       </c>
     </row>
@@ -1878,7 +2240,7 @@
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>## Construction</t>
+          <t>---</t>
         </is>
       </c>
     </row>
@@ -1890,7 +2252,7 @@
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>### S512-A (book period, 1948-1989)</t>
+          <t>## Construction</t>
         </is>
       </c>
     </row>
@@ -1902,35 +2264,35 @@
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1. Read `data/source/book_tables/Table5_7_KeyRatios.csv`.</t>
+          <t>### S512-A (book period, 1948-1989)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>2. Extract column `T512A` (book-authoritative values; the `T512` column without the A-suffix is the replicator-recomputed comparison and is not used here).</t>
-        </is>
-      </c>
+      <c r="B53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>3. No further transformation — this is the canonical published value.</t>
+          <t>1. Read `data/source/book_tables/Table5_7_KeyRatios.csv`.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
-      <c r="B55" t="inlineStr"/>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2. Extract column `T512A` (book-authoritative values; the `T512` column without the A-suffix is the replicator-recomputed comparison and is not used here).</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Validator checks the loaded series against the published benchmark years from validation_config.json.</t>
+          <t>3. No further transformation — this is the canonical published value.</t>
         </is>
       </c>
     </row>
@@ -1942,7 +2304,7 @@
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>Validator checks the loaded series against the published benchmark years from validation_config.json.</t>
         </is>
       </c>
     </row>
@@ -1954,7 +2316,7 @@
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
-          <t>## Reference Values (Validation Benchmarks)</t>
+          <t>### S512-INTERP (1990-1997 bridge)</t>
         </is>
       </c>
     </row>
@@ -1966,67 +2328,79 @@
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t>1948=0.54, 1958=0.49, 1967=0.452, 1977=0.412, 1989=0.36</t>
+          <t>**1990-1997 bridge**: log-linear interpolation between the book 1989 endpoint</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr"/>
-      <c r="B63" t="inlineStr"/>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>(`S512-A[1989]` = 0.3600) and the BEA-derived first-EXT value</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Tolerance class: `share_series` (rel 0.05 / abs 0.02).</t>
+          <t>(`S512-EXT[1998]` = 0.3195), consistent with the S501–S503 bridge per</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr"/>
-      <c r="B65" t="inlineStr"/>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>`Technical/Build/BUILD_NARRATIVE.md` Stage 5 cohort 3.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr"/>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Validator: `code/V03_validators/V03_S512_productive_wage_share.py` writes to `data/intermediate/validation/S512.json`.</t>
-        </is>
-      </c>
+      <c r="B66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr"/>
-      <c r="B67" t="inlineStr"/>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Formula: `v(t) = exp( ln(v0) + (t - 1989)/(1998 - 1989) · (ln(v1) - ln(v0)) )`</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr"/>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="B68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr"/>
-      <c r="B69" t="inlineStr"/>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>These eight values are **INTERPOLATED estimates**, not directly observed.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
-          <t>## Provenance Chain</t>
+          <t>The Marxian productive/unproductive partition cannot be reconstructed cleanly</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr"/>
-      <c r="B71" t="inlineStr"/>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>on a NAICS basis for 1990-1997 (BEA NIPA 6.2D begins 1998; pre-2002 BLS CES</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
-          <t>```</t>
+          <t>is SIC-only). Documentation script: `code/M04_manual/M04_S512_1990_1997_bridge.py`</t>
         </is>
       </c>
     </row>
@@ -2034,39 +2408,31 @@
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr">
         <is>
-          <t>data/source/book_tables/Table5_7_KeyRatios.csv</t>
+          <t>(also acts as a verifier). Sample values: 1991 = 0.3506, 1995 = 0.3325.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr"/>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  └── code/L01_loaders/L01_S512_productive_wage_share.py</t>
-        </is>
-      </c>
+      <c r="B74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr">
         <is>
-          <t xml:space="preserve">       └── data/intermediate/S512.csv</t>
+          <t>### S512-EXT (1998-2024)</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr"/>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            └── code/P02_processors/P02_S512_productive_wage_share.py</t>
-        </is>
-      </c>
+      <c r="B76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr">
         <is>
-          <t xml:space="preserve">                 └── data/final/S512.csv</t>
+          <t>BEA NIPA 6.2D productive-sector compensation / total compensation,</t>
         </is>
       </c>
     </row>
@@ -2074,7 +2440,7 @@
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr">
         <is>
-          <t xml:space="preserve">                      └── code/V03_validators/V03_S512_productive_wage_share.py</t>
+          <t>level-spliced to the book endpoint at 1989. Begins 1998 because that is</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2448,7 @@
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="inlineStr">
         <is>
-          <t>```</t>
+          <t>when NIPA 6.2D series begins.</t>
         </is>
       </c>
     </row>
@@ -2094,7 +2460,7 @@
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>### S512-COMBINED</t>
         </is>
       </c>
     </row>
@@ -2106,41 +2472,257 @@
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="inlineStr">
         <is>
-          <t>## Citations</t>
+          <t>Concatenation: 1948-1989 from S512-A, 1990-1997 from S512-INTERP (bridge),</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr"/>
-      <c r="B84" t="inlineStr"/>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>1998-2024 from S512-EXT.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr"/>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. *Measuring the Wealth of Nations: The Political Economy of National Accounts*. Cambridge University Press. Table 5.7 (Key Ratios), Chapter 5.</t>
-        </is>
-      </c>
+      <c r="B85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr"/>
-      <c r="B86" t="inlineStr"/>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>### Downstream impact</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr"/>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="B87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr"/>
-      <c r="B88" t="inlineStr"/>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>S504 (Variable Capital) is derived as V* = S512 · W, so the 1990-1997</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="inlineStr">
+        <is>
+          <t>S512-INTERP values propagate into S504-INTERP across the same years.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr"/>
+      <c r="B90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr"/>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr"/>
+      <c r="B92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr"/>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>## Reference Values (Validation Benchmarks)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr"/>
+      <c r="B94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr"/>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>1948=0.54, 1958=0.49, 1967=0.452, 1977=0.412, 1989=0.36</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr"/>
+      <c r="B96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr"/>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Tolerance class: `share_series` (rel 0.05 / abs 0.02).</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr"/>
+      <c r="B98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr"/>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Validator: `code/V03_validators/V03_S512_productive_wage_share.py` writes to `data/intermediate/validation/S512.json`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr"/>
+      <c r="B100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr"/>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr"/>
+      <c r="B102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr"/>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>## Provenance Chain</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr"/>
+      <c r="B104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr"/>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>```</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr"/>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>data/source/book_tables/Table5_7_KeyRatios.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr"/>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  └── code/L01_loaders/L01_S512_productive_wage_share.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr"/>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       └── data/intermediate/S512.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr"/>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            └── code/P02_processors/P02_S512_productive_wage_share.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr"/>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                 └── data/final/S512.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr"/>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                      └── code/V03_validators/V03_S512_productive_wage_share.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr"/>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>```</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr"/>
+      <c r="B113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr"/>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr"/>
+      <c r="B115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr"/>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>## Citations</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr"/>
+      <c r="B117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr"/>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. *Measuring the Wealth of Nations: The Political Economy of National Accounts*. Cambridge University Press. Table 5.7 (Key Ratios), Chapter 5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr"/>
+      <c r="B119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr"/>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr"/>
+      <c r="B121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr"/>
+      <c r="B122" t="inlineStr">
         <is>
           <t>*Generated by anu-ingestion (re-authored from scratch against the Anu Framework v10.0 standard).*</t>
         </is>
@@ -2421,7 +3003,7 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
-        <v>140</v>
+        <v>151</v>
       </c>
     </row>
     <row r="20">
@@ -2551,7 +3133,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2758,38 +3340,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{"1948": 0.54, "1958": 0.49, "1967": 0.42, "1977": 0.412, "1989": 0.36}</t>
+          <t>{"1948": 0.54, "1958": 0.44, "1967": 0.42, "1977": 0.412, "1989": 0.36}</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>expected_range</t>
+          <t>v1.3_patch</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>[0.1, 0.8]</t>
+          <t>DIV-016: corrected stale interpolated mid-year refval 1958 (0.49-&gt;0.44) to panel V_over_W (Table 5.7 family) value. Other anchors unchanged (already match).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>tolerance</t>
+          <t>expected_range</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>share_series</t>
+          <t>[0.1, 0.8]</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>tolerance_class</t>
+          <t>tolerance</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2801,72 +3383,96 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>tolerance_rel</t>
+          <t>tolerance_class</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>share_series</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>tolerance_abs</t>
+          <t>tolerance_rel</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.05</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>source_table</t>
+          <t>tolerance_abs</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Table 5.14, p.140</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>previous_1967_value</t>
+          <t>source_table</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0.452</t>
+          <t>Table 5.14, p.140</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>previous_1967_source</t>
+          <t>previous_1967_value</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>code-derived (pre-v1.0, linear interpolation in Table5_7_KeyRatios.csv)</t>
+          <t>0.452</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>previous_1967_source</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>code-derived (pre-v1.0, linear interpolation in Table5_7_KeyRatios.csv)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>notes</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>1967 midpoint anchor corrected from code-derived 0.452 (registry rounded to 0.45 in hyper-review notes) to book Table 5.14 value 0.42. Endpoints 1948/1989 preserved from Table 5.7. Drift documented in DIV-006. Note: 1958/1977 intermediate values remain code-derived linear interpolations from Table 5.7 source CSV; only the 1967 midpoint has a directly-quoted book anchor in Table 5.14 (p.140).</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>extension_year_range</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>[1948, 2024]</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S512.xlsx
+++ b/extenbooks/S512.xlsx
@@ -454,7 +454,7 @@
     <col width="31" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="62" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -480,7 +480,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>derived, units=per_subseries</t>
+          <t>BLS CES + BEA NIPA (level-splice ~1.17x), units=per_subseries</t>
         </is>
       </c>
     </row>
@@ -507,7 +507,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>S512-INTERP</t>
+          <t>S512-EXT-SPLICED-DEPRECATED</t>
         </is>
       </c>
     </row>
@@ -1233,13 +1233,13 @@
         <v/>
       </c>
       <c r="C45" s="3" t="n">
-        <v>0.3546981726853149</v>
+        <v>0.3410014390608473</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v/>
+        <v>0.3410014390608473</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>0.3546981726853149</v>
+        <v/>
       </c>
     </row>
     <row r="46">
@@ -1250,13 +1250,13 @@
         <v/>
       </c>
       <c r="C46" s="3" t="n">
-        <v>0.3494744269619487</v>
+        <v>0.3322703039197615</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v/>
+        <v>0.3322703039197615</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>0.3494744269619487</v>
+        <v/>
       </c>
     </row>
     <row r="47">
@@ -1267,13 +1267,13 @@
         <v/>
       </c>
       <c r="C47" s="3" t="n">
-        <v>0.34432761289903</v>
+        <v>0.3229505327614342</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v/>
+        <v>0.3229505327614342</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>0.34432761289903</v>
+        <v/>
       </c>
     </row>
     <row r="48">
@@ -1284,13 +1284,13 @@
         <v/>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.3392565975010623</v>
+        <v>0.3222044958596282</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v/>
+        <v>0.3222044958596282</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.3392565975010623</v>
+        <v/>
       </c>
     </row>
     <row r="49">
@@ -1301,13 +1301,13 @@
         <v/>
       </c>
       <c r="C49" s="3" t="n">
-        <v>0.3342602644585117</v>
+        <v>0.3259986041607591</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v/>
+        <v>0.3259986041607591</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>0.3342602644585117</v>
+        <v/>
       </c>
     </row>
     <row r="50">
@@ -1318,13 +1318,13 @@
         <v/>
       </c>
       <c r="C50" s="3" t="n">
-        <v>0.3293375139020673</v>
+        <v>0.3219165486764451</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v/>
+        <v>0.3219165486764451</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>0.3293375139020673</v>
+        <v/>
       </c>
     </row>
     <row r="51">
@@ -1335,13 +1335,13 @@
         <v/>
       </c>
       <c r="C51" s="3" t="n">
-        <v>0.3244872621605218</v>
+        <v>0.3161886662763514</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v/>
+        <v>0.3161886662763514</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>0.3244872621605218</v>
+        <v/>
       </c>
     </row>
     <row r="52">
@@ -1352,13 +1352,13 @@
         <v/>
       </c>
       <c r="C52" s="3" t="n">
-        <v>0.3197084415222162</v>
+        <v>0.3135910115871966</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v/>
+        <v>0.3135910115871966</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>0.3197084415222162</v>
+        <v/>
       </c>
     </row>
     <row r="53">
@@ -1369,13 +1369,13 @@
         <v/>
       </c>
       <c r="C53" s="3" t="n">
+        <v>0.2692202420837295</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>0.2692202420837295</v>
+      </c>
+      <c r="E53" s="3" t="n">
         <v>0.3149999999999999</v>
-      </c>
-      <c r="D53" s="3" t="n">
-        <v>0.3149999999999999</v>
-      </c>
-      <c r="E53" s="3" t="n">
-        <v/>
       </c>
     </row>
     <row r="54">
@@ -1386,13 +1386,13 @@
         <v/>
       </c>
       <c r="C54" s="3" t="n">
+        <v>0.2667019824598227</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>0.2667019824598227</v>
+      </c>
+      <c r="E54" s="3" t="n">
         <v>0.3120535210302502</v>
-      </c>
-      <c r="D54" s="3" t="n">
-        <v>0.3120535210302502</v>
-      </c>
-      <c r="E54" s="3" t="n">
-        <v/>
       </c>
     </row>
     <row r="55">
@@ -1403,13 +1403,13 @@
         <v/>
       </c>
       <c r="C55" s="3" t="n">
+        <v>0.262657371647638</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>0.262657371647638</v>
+      </c>
+      <c r="E55" s="3" t="n">
         <v>0.3073211413400116</v>
-      </c>
-      <c r="D55" s="3" t="n">
-        <v>0.3073211413400116</v>
-      </c>
-      <c r="E55" s="3" t="n">
-        <v/>
       </c>
     </row>
     <row r="56">
@@ -1420,13 +1420,13 @@
         <v/>
       </c>
       <c r="C56" s="3" t="n">
+        <v>0.2531617919338203</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>0.2531617919338203</v>
+      </c>
+      <c r="E56" s="3" t="n">
         <v>0.2962108786543316</v>
-      </c>
-      <c r="D56" s="3" t="n">
-        <v>0.2962108786543316</v>
-      </c>
-      <c r="E56" s="3" t="n">
-        <v/>
       </c>
     </row>
     <row r="57">
@@ -1437,13 +1437,13 @@
         <v/>
       </c>
       <c r="C57" s="3" t="n">
+        <v>0.2430502117727214</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>0.2430502117727214</v>
+      </c>
+      <c r="E57" s="3" t="n">
         <v>0.2843798672634588</v>
-      </c>
-      <c r="D57" s="3" t="n">
-        <v>0.2843798672634588</v>
-      </c>
-      <c r="E57" s="3" t="n">
-        <v/>
       </c>
     </row>
     <row r="58">
@@ -1454,13 +1454,13 @@
         <v/>
       </c>
       <c r="C58" s="3" t="n">
+        <v>0.2365555874884278</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>0.2365555874884278</v>
+      </c>
+      <c r="E58" s="3" t="n">
         <v>0.2767808597233192</v>
-      </c>
-      <c r="D58" s="3" t="n">
-        <v>0.2767808597233192</v>
-      </c>
-      <c r="E58" s="3" t="n">
-        <v/>
       </c>
     </row>
     <row r="59">
@@ -1471,13 +1471,13 @@
         <v/>
       </c>
       <c r="C59" s="3" t="n">
+        <v>0.2340961097035964</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>0.2340961097035964</v>
+      </c>
+      <c r="E59" s="3" t="n">
         <v>0.2739031581945428</v>
-      </c>
-      <c r="D59" s="3" t="n">
-        <v>0.2739031581945428</v>
-      </c>
-      <c r="E59" s="3" t="n">
-        <v/>
       </c>
     </row>
     <row r="60">
@@ -1488,13 +1488,13 @@
         <v/>
       </c>
       <c r="C60" s="3" t="n">
+        <v>0.2320904565979541</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>0.2320904565979541</v>
+      </c>
+      <c r="E60" s="3" t="n">
         <v>0.2715564523027888</v>
-      </c>
-      <c r="D60" s="3" t="n">
-        <v>0.2715564523027888</v>
-      </c>
-      <c r="E60" s="3" t="n">
-        <v/>
       </c>
     </row>
     <row r="61">
@@ -1505,13 +1505,13 @@
         <v/>
       </c>
       <c r="C61" s="3" t="n">
+        <v>0.2307644074422475</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>0.2307644074422475</v>
+      </c>
+      <c r="E61" s="3" t="n">
         <v>0.2700049141241785</v>
-      </c>
-      <c r="D61" s="3" t="n">
-        <v>0.2700049141241785</v>
-      </c>
-      <c r="E61" s="3" t="n">
-        <v/>
       </c>
     </row>
     <row r="62">
@@ -1522,13 +1522,13 @@
         <v/>
       </c>
       <c r="C62" s="3" t="n">
+        <v>0.2272889106077001</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>0.2272889106077001</v>
+      </c>
+      <c r="E62" s="3" t="n">
         <v>0.2659384238246046</v>
-      </c>
-      <c r="D62" s="3" t="n">
-        <v>0.2659384238246046</v>
-      </c>
-      <c r="E62" s="3" t="n">
-        <v/>
       </c>
     </row>
     <row r="63">
@@ -1539,13 +1539,13 @@
         <v/>
       </c>
       <c r="C63" s="3" t="n">
+        <v>0.2217082756907</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>0.2217082756907</v>
+      </c>
+      <c r="E63" s="3" t="n">
         <v>0.2594088256589946</v>
-      </c>
-      <c r="D63" s="3" t="n">
-        <v>0.2594088256589946</v>
-      </c>
-      <c r="E63" s="3" t="n">
-        <v/>
       </c>
     </row>
     <row r="64">
@@ -1556,13 +1556,13 @@
         <v/>
       </c>
       <c r="C64" s="3" t="n">
+        <v>0.2064572853862067</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>0.2064572853862067</v>
+      </c>
+      <c r="E64" s="3" t="n">
         <v>0.2415644692735586</v>
-      </c>
-      <c r="D64" s="3" t="n">
-        <v>0.2415644692735586</v>
-      </c>
-      <c r="E64" s="3" t="n">
-        <v/>
       </c>
     </row>
     <row r="65">
@@ -1573,13 +1573,13 @@
         <v/>
       </c>
       <c r="C65" s="3" t="n">
+        <v>0.2015668923428044</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>0.2015668923428044</v>
+      </c>
+      <c r="E65" s="3" t="n">
         <v>0.2358424856784595</v>
-      </c>
-      <c r="D65" s="3" t="n">
-        <v>0.2358424856784595</v>
-      </c>
-      <c r="E65" s="3" t="n">
-        <v/>
       </c>
     </row>
     <row r="66">
@@ -1590,13 +1590,13 @@
         <v/>
       </c>
       <c r="C66" s="3" t="n">
+        <v>0.2022947481666752</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>0.2022947481666752</v>
+      </c>
+      <c r="E66" s="3" t="n">
         <v>0.2366941102916192</v>
-      </c>
-      <c r="D66" s="3" t="n">
-        <v>0.2366941102916192</v>
-      </c>
-      <c r="E66" s="3" t="n">
-        <v/>
       </c>
     </row>
     <row r="67">
@@ -1607,13 +1607,13 @@
         <v/>
       </c>
       <c r="C67" s="3" t="n">
+        <v>0.2038195416722741</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>0.2038195416722741</v>
+      </c>
+      <c r="E67" s="3" t="n">
         <v>0.2384781884521101</v>
-      </c>
-      <c r="D67" s="3" t="n">
-        <v>0.2384781884521101</v>
-      </c>
-      <c r="E67" s="3" t="n">
-        <v/>
       </c>
     </row>
     <row r="68">
@@ -1624,13 +1624,13 @@
         <v/>
       </c>
       <c r="C68" s="3" t="n">
+        <v>0.203507307664403</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>0.203507307664403</v>
+      </c>
+      <c r="E68" s="3" t="n">
         <v>0.2381128603782693</v>
-      </c>
-      <c r="D68" s="3" t="n">
-        <v>0.2381128603782693</v>
-      </c>
-      <c r="E68" s="3" t="n">
-        <v/>
       </c>
     </row>
     <row r="69">
@@ -1641,13 +1641,13 @@
         <v/>
       </c>
       <c r="C69" s="3" t="n">
+        <v>0.2051437113630309</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>0.2051437113630309</v>
+      </c>
+      <c r="E69" s="3" t="n">
         <v>0.2400275275707439</v>
-      </c>
-      <c r="D69" s="3" t="n">
-        <v>0.2400275275707439</v>
-      </c>
-      <c r="E69" s="3" t="n">
-        <v/>
       </c>
     </row>
     <row r="70">
@@ -1658,13 +1658,13 @@
         <v/>
       </c>
       <c r="C70" s="3" t="n">
+        <v>0.2043042990513143</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>0.2043042990513143</v>
+      </c>
+      <c r="E70" s="3" t="n">
         <v>0.2390453767631218</v>
-      </c>
-      <c r="D70" s="3" t="n">
-        <v>0.2390453767631218</v>
-      </c>
-      <c r="E70" s="3" t="n">
-        <v/>
       </c>
     </row>
     <row r="71">
@@ -1675,13 +1675,13 @@
         <v/>
       </c>
       <c r="C71" s="3" t="n">
+        <v>0.2023353549851155</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>0.2023353549851155</v>
+      </c>
+      <c r="E71" s="3" t="n">
         <v>0.2367416221269466</v>
-      </c>
-      <c r="D71" s="3" t="n">
-        <v>0.2367416221269466</v>
-      </c>
-      <c r="E71" s="3" t="n">
-        <v/>
       </c>
     </row>
     <row r="72">
@@ -1692,13 +1692,13 @@
         <v/>
       </c>
       <c r="C72" s="3" t="n">
+        <v>0.2029082423382435</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>0.2029082423382435</v>
+      </c>
+      <c r="E72" s="3" t="n">
         <v>0.2374119265395665</v>
-      </c>
-      <c r="D72" s="3" t="n">
-        <v>0.2374119265395665</v>
-      </c>
-      <c r="E72" s="3" t="n">
-        <v/>
       </c>
     </row>
     <row r="73">
@@ -1709,13 +1709,13 @@
         <v/>
       </c>
       <c r="C73" s="3" t="n">
+        <v>0.2041833083821679</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>0.2041833083821679</v>
+      </c>
+      <c r="E73" s="3" t="n">
         <v>0.2389038121449262</v>
-      </c>
-      <c r="D73" s="3" t="n">
-        <v>0.2389038121449262</v>
-      </c>
-      <c r="E73" s="3" t="n">
-        <v/>
       </c>
     </row>
     <row r="74">
@@ -1726,13 +1726,13 @@
         <v/>
       </c>
       <c r="C74" s="3" t="n">
+        <v>0.2045711171629751</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>0.2045711171629751</v>
+      </c>
+      <c r="E74" s="3" t="n">
         <v>0.2393575661606301</v>
-      </c>
-      <c r="D74" s="3" t="n">
-        <v>0.2393575661606301</v>
-      </c>
-      <c r="E74" s="3" t="n">
-        <v/>
       </c>
     </row>
     <row r="75">
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="C75" s="3" t="n">
+        <v>0.1997251627804394</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>0.1997251627804394</v>
+      </c>
+      <c r="E75" s="3" t="n">
         <v>0.233687577831803</v>
-      </c>
-      <c r="D75" s="3" t="n">
-        <v>0.233687577831803</v>
-      </c>
-      <c r="E75" s="3" t="n">
-        <v/>
       </c>
     </row>
     <row r="76">
@@ -1760,13 +1760,13 @@
         <v/>
       </c>
       <c r="C76" s="3" t="n">
+        <v>0.1964877777967116</v>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>0.1964877777967116</v>
+      </c>
+      <c r="E76" s="3" t="n">
         <v>0.2298996892912486</v>
-      </c>
-      <c r="D76" s="3" t="n">
-        <v>0.2298996892912486</v>
-      </c>
-      <c r="E76" s="3" t="n">
-        <v/>
       </c>
     </row>
     <row r="77">
@@ -1777,13 +1777,13 @@
         <v/>
       </c>
       <c r="C77" s="3" t="n">
+        <v>0.1988052555544637</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>0.1988052555544637</v>
+      </c>
+      <c r="E77" s="3" t="n">
         <v>0.2326112442918747</v>
-      </c>
-      <c r="D77" s="3" t="n">
-        <v>0.2326112442918747</v>
-      </c>
-      <c r="E77" s="3" t="n">
-        <v/>
       </c>
     </row>
     <row r="78">
@@ -1794,13 +1794,13 @@
         <v/>
       </c>
       <c r="C78" s="3" t="n">
+        <v>0.1986883870953665</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>0.1986883870953665</v>
+      </c>
+      <c r="E78" s="3" t="n">
         <v>0.2324745028480268</v>
-      </c>
-      <c r="D78" s="3" t="n">
-        <v>0.2324745028480268</v>
-      </c>
-      <c r="E78" s="3" t="n">
-        <v/>
       </c>
     </row>
     <row r="79">
@@ -1811,13 +1811,13 @@
         <v/>
       </c>
       <c r="C79" s="3" t="n">
+        <v>0.1980497980343326</v>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>0.1980497980343326</v>
+      </c>
+      <c r="E79" s="3" t="n">
         <v>0.2317273244313195</v>
-      </c>
-      <c r="D79" s="3" t="n">
-        <v>0.2317273244313195</v>
-      </c>
-      <c r="E79" s="3" t="n">
-        <v/>
       </c>
     </row>
   </sheetData>
@@ -1831,10 +1831,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B122"/>
+  <dimension ref="A1:B131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -2042,12 +2042,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S512-INTERP</t>
+          <t>S512-EXT-SPLICED-DEPRECATED</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>BLS CES + BEA NIPA (level-splice ~1.17x)</t>
         </is>
       </c>
     </row>
@@ -2725,6 +2725,70 @@
       <c r="B122" t="inlineStr">
         <is>
           <t>*Generated by anu-ingestion (re-authored from scratch against the Anu Framework v10.0 standard).*</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr"/>
+      <c r="B123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr"/>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr"/>
+      <c r="B125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr"/>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>## WP-A REBUILD ADDENDUM (2026-07-01, comprehensive review)</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr"/>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>**De-spliced (R1) + real SIC fill (R3), DIV-A11/A12.** S512-EXT is now the honest raw share:</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr"/>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>SIC comp_prod/T20100 1990-97 (0.341-&gt;0.314) + raw NIPA 6.2D lines[5,7,11,12,13,43]/line1</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr"/>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>1998-2024 (0.269-&gt;0.198). The old level-splice (scale~1.17 to projected-book 0.315) is retained</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr"/>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>as S512-EXT-SPLICED-DEPRECATED. S512-INTERP retired. The SIC-&gt;NAICS break 0.314-&gt;0.269 at</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr"/>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>1997/98 is REAL and disclosed (DIV-010), not spliced away. V03 PASS 5/5.</t>
         </is>
       </c>
     </row>
@@ -3271,7 +3335,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>none (de-spliced raw share; R1; DIV-029)</t>
         </is>
       </c>
     </row>
